--- a/Data/Home/BedroomTwo.Humidifier001.xlsx
+++ b/Data/Home/BedroomTwo.Humidifier001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709270046</v>
+        <v>1711842748</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709281585</v>
+        <v>1711845274</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709256942</v>
+        <v>1711927678</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709267058</v>
+        <v>1711930015</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709345903</v>
+        <v>1712455573</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709359075</v>
+        <v>1712457250</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709438404</v>
+        <v>1712621662</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709451756</v>
+        <v>1712623991</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709514398</v>
+        <v>1712705793</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709527015</v>
+        <v>1712708142</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709615736</v>
+        <v>1712791559</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709631111</v>
+        <v>1712793882</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709869507</v>
+        <v>1712973208</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709880643</v>
+        <v>1712974786</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709950227</v>
+        <v>1713137752</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709962504</v>
+        <v>1713140124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1710038667</v>
+        <v>1713224109</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1710050866</v>
+        <v>1713226482</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1710132655</v>
+        <v>1713236203</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1150,9 +1173,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1710148117</v>
+        <v>1713314487</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1710210167</v>
+        <v>1713322304</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1222,9 +1247,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1710223058</v>
+        <v>1713398946</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1710473105</v>
+        <v>1713415784</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1294,9 +1321,10 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1710484760</v>
+        <v>1713485913</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1710560898</v>
+        <v>1713494394</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1366,9 +1395,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1710573853</v>
+        <v>1713580116</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1710642417</v>
+        <v>1713752556</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1438,9 +1469,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710658070</v>
+        <v>1713832789</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710725622</v>
+        <v>1713839133</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1510,9 +1543,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710737488</v>
+        <v>1713917539</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710814662</v>
+        <v>1713933561</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1582,9 +1617,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710827908</v>
+        <v>1714006224</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,366 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1711075493</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1711089193</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1711160565</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1711171752</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1711257901</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1711271192</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1711338905</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1711357486</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1711435408</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: on</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Humidifier_Operation</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1711451448</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidifier001.state: off</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
